--- a/2nd_round_screening/Table.xlsx
+++ b/2nd_round_screening/Table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,42 +441,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>LL2</t>
+          <t>SL1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>LL3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>Concentration (µg/mL)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Concentration (µg/mL)</t>
+          <t>Size (nm)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Size (nm)</t>
+          <t>PDI</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>PDI</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Zeta potential (mV)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -491,46 +491,46 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.125%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0.125%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>410.68 ± 14.08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>108.95 ± 20.31</t>
+          <t>109.09 ± 2.61</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30.22 ± 0.59</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.2 ± 0.01</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
+          <t>0.18 ± 0.02</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-28.4 ± 1.07</t>
+        </is>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -542,49 +542,49 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.250%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>0.250%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>403.74 ± 7.33</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1128.34 ± 36.84</t>
+          <t>107.19 ± 0.92</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28.61 ± 0.56</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.15 ± 0.03</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+          <t>0.18 ± 0.03</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-25.57 ± 1.21</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -593,46 +593,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>396.67 ± 6.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>952.84 ± 5.13</t>
+          <t>110.0 ± 3.69</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>27.68 ± 0.58</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.18 ± 0.01</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
+          <t>0.16 ± 0.02</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-30.08 ± 1.11</t>
+        </is>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -644,49 +644,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0.125%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0.250%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>611.69 ± 27.08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1137.3 ± 20.36</t>
+          <t>104.27 ± 3.2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>55.35 ± 2.07</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.32 ± 0.01</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+          <t>0.17 ± 0.02</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-26.66 ± 2.66</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -695,49 +695,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0.250%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>669.97 ± 16.86</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>989.99 ± 14.87</t>
+          <t>99.7 ± 3.93</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>45.92 ± 1.65</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.39 ± 0.02</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
+          <t>0.16 ± 0.02</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-23.63 ± 2.63</t>
+        </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -746,46 +746,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0.125%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>677.91 ± 3.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>967.51 ± 8.86</t>
+          <t>114.55 ± 4.3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>90.24 ± 2.73</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.25 ± 0.02</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
+          <t>0.13 ± 0.02</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-24.33 ± 1.23</t>
+        </is>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -797,49 +797,49 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0.125%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>895.86 ± 15.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>547.94 ± 11.66</t>
+          <t>94.1 ± 2.26</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>79.3 ± 1.2</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
           <t>0.18 ± 0.02</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-24.69 ± 2.35</t>
+        </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -848,46 +848,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.250%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>0.125%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>924.23 ± 5.84</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1154.62 ± 5.23</t>
+          <t>102.87 ± 1.71</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>64.22 ± 2.08</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.34 ± 0.02</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
+          <t>0.16 ± 0.01</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-28.58 ± 1.06</t>
+        </is>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -899,610 +899,49 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>0.250%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>922.35 ± 12.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1014.19 ± 12.45</t>
+          <t>110.13 ± 3.36</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>60.42 ± 5.49</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.42 ± 0.12</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
+          <t>0.13 ± 0.01</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-25.86 ± 1.38</t>
+        </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.75%</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1019.18 ± 24.63</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>102.12 ± 1.94</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.22 ± 0.02</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>548.8 ± 6.17</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>85.01 ± 2.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.14 ± 0.01</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>560.84 ± 6.56</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>98.96 ± 26.93</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.15 ± 0.02</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>394.89 ± 6.13</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>114.81 ± 5.05</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.15 ± 0.04</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0.75%</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>978.75 ± 10.62</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>96.69 ± 12.01</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.18 ± 0.01</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>555.78 ± 8.28</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>90.73 ± 1.24</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.17 ± 0.03</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>569.45 ± 3.18</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>132.28 ± 1.92</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.14 ± 0.03</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>394.7 ± 5.57</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>132.23 ± 4.9</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.13 ± 0.01</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>578.11 ± 5.55</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>167.9 ± 9.81</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.11 ± 0.0</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>401.5 ± 6.32</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>159.17 ± 3.31</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0.13 ± 0.01</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0.75%</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>186.66 ± 2.26</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>147.96 ± 3.18</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.15 ± 0.03</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/2nd_round_screening/Table.xlsx
+++ b/2nd_round_screening/Table.xlsx
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
